--- a/artfynd/A 24352-2026 artfynd.xlsx
+++ b/artfynd/A 24352-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134670866</v>
+        <v>134669811</v>
       </c>
       <c r="B2" t="n">
         <v>57972</v>
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502948</v>
+        <v>503060</v>
       </c>
       <c r="R2" t="n">
-        <v>6638715</v>
+        <v>6638653</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hack i levande (än så länge) gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,23 +776,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134670904</v>
+        <v>134670866</v>
       </c>
       <c r="B3" t="n">
         <v>57972</v>
@@ -827,7 +857,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502944</v>
+        <v>502948</v>
       </c>
       <c r="R3" t="n">
         <v>6638715</v>
@@ -862,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födohack vid basen av gran</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134670556</v>
+        <v>134670904</v>
       </c>
       <c r="B4" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,27 +940,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502919</v>
+        <v>502944</v>
       </c>
       <c r="R4" t="n">
-        <v>6638637</v>
+        <v>6638715</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -979,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +1014,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Och äldre spillning på samma sten.</t>
+          <t>Födohack vid basen av gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134669830</v>
+        <v>134670556</v>
       </c>
       <c r="B5" t="n">
-        <v>4776</v>
+        <v>57162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,27 +1057,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503026</v>
+        <v>502919</v>
       </c>
       <c r="R5" t="n">
-        <v>6638664</v>
+        <v>6638637</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1096,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Och kläckhål.</t>
+          <t>Och äldre spillning på samma sten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134669919</v>
+        <v>134669830</v>
       </c>
       <c r="B6" t="n">
-        <v>5201</v>
+        <v>4776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,21 +1174,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502999</v>
+        <v>503026</v>
       </c>
       <c r="R6" t="n">
-        <v>6638667</v>
+        <v>6638664</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1213,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1248,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Och kläckhål.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134670173</v>
+        <v>134669919</v>
       </c>
       <c r="B7" t="n">
         <v>5201</v>
@@ -1290,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502895</v>
+        <v>502999</v>
       </c>
       <c r="R7" t="n">
-        <v>6638548</v>
+        <v>6638667</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1325,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134669841</v>
+        <v>134670173</v>
       </c>
       <c r="B8" t="n">
-        <v>99112</v>
+        <v>5201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,36 +1403,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503017</v>
+        <v>502895</v>
       </c>
       <c r="R8" t="n">
-        <v>6638670</v>
+        <v>6638548</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1446,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,7 +1504,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134669991</v>
+        <v>134669841</v>
       </c>
       <c r="B9" t="n">
         <v>99112</v>
@@ -1513,7 +1534,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1532,10 +1553,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502988</v>
+        <v>503017</v>
       </c>
       <c r="R9" t="n">
-        <v>6638648</v>
+        <v>6638670</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1567,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1598,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,7 +1625,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134670028</v>
+        <v>134669991</v>
       </c>
       <c r="B10" t="n">
         <v>99112</v>
@@ -1634,7 +1655,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1653,10 +1674,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502986</v>
+        <v>502988</v>
       </c>
       <c r="R10" t="n">
-        <v>6638620</v>
+        <v>6638648</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1688,7 +1709,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1719,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,7 +1746,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134670879</v>
+        <v>134670028</v>
       </c>
       <c r="B11" t="n">
         <v>99112</v>
@@ -1755,7 +1776,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1774,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502945</v>
+        <v>502986</v>
       </c>
       <c r="R11" t="n">
-        <v>6638713</v>
+        <v>6638620</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1809,7 +1830,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1819,7 +1840,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,6 +1864,127 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134670879</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tys-Olles berg, Tys-Olles berg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>502945</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6638713</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24352-2026 artfynd.xlsx
+++ b/artfynd/A 24352-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -814,6 +819,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669811</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670866</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670904</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1160,6 +1180,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670556</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669830</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1389,6 +1419,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669919</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1501,6 +1536,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670173</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1622,6 +1662,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669841</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1743,6 +1788,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134669991</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1864,6 +1914,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670028</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1985,8 +2040,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670879</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>